--- a/static/docs/AMA_uitslagen amateuvoetbal 2025-2026 definitief.xlsx
+++ b/static/docs/AMA_uitslagen amateuvoetbal 2025-2026 definitief.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mediahuis-my.sharepoint.com/personal/torsten_faruhn_delimburger_nl/Documents/Torsten/CUE Print/amateur- en regiosport nieuwe stijl/uitslagendienst/amateurvoetbal/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="96" documentId="8_{F6EDDE6E-FDD8-41E1-97DF-2A01485E9FFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D3385A3-6BC1-48B5-B725-04AE0A3C2245}"/>
+  <xr:revisionPtr revIDLastSave="97" documentId="8_{F6EDDE6E-FDD8-41E1-97DF-2A01485E9FFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41B6E541-415D-4507-A82C-AE8B4388D799}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INVOER" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="863" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="314">
   <si>
     <t>KLASSE</t>
   </si>
@@ -3183,9 +3183,7 @@
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" s="4"/>
-      <c r="B67" s="3" t="s">
-        <v>165</v>
-      </c>
+      <c r="B67" s="3"/>
       <c r="C67" s="2"/>
       <c r="D67" s="3"/>
       <c r="E67" s="2"/>

--- a/static/docs/AMA_uitslagen amateuvoetbal 2025-2026 definitief.xlsx
+++ b/static/docs/AMA_uitslagen amateuvoetbal 2025-2026 definitief.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mediahuis-my.sharepoint.com/personal/torsten_faruhn_delimburger_nl/Documents/Torsten/CUE Print/amateur- en regiosport nieuwe stijl/uitslagendienst/amateurvoetbal/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="97" documentId="8_{F6EDDE6E-FDD8-41E1-97DF-2A01485E9FFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41B6E541-415D-4507-A82C-AE8B4388D799}"/>
+  <xr:revisionPtr revIDLastSave="102" documentId="8_{F6EDDE6E-FDD8-41E1-97DF-2A01485E9FFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3EBEF0B9-02C7-4F88-AD7C-181575E213BE}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
     <definedName name="VIERDE_KLASSE_C">FORMULE!$X$2:$X$22</definedName>
     <definedName name="VIERDE_KLASSE_D">FORMULE!$Z$2:$Z$22</definedName>
     <definedName name="VIERDE_KLASSE_F">FORMULE!$AB$2:$AB$22</definedName>
-    <definedName name="VIERDE_KLASSE_G">FORMULE!$AD$2:$AD$22</definedName>
+    <definedName name="VIERDE_KLASSE_G">FORMULE!$AD$2:$AD$23</definedName>
     <definedName name="VIJFDE_KLASSE_A">FORMULE!$AF$2:$AF$22</definedName>
     <definedName name="VIJFDE_KLASSE_B">FORMULE!$AH$2:$AH$22</definedName>
     <definedName name="VIJFDE_KLASSE_C">FORMULE!$AJ$2:$AJ$22</definedName>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="313">
   <si>
     <t>KLASSE</t>
   </si>
@@ -649,9 +649,6 @@
   </si>
   <si>
     <t>Nuenen</t>
-  </si>
-  <si>
-    <t>SSS;18</t>
   </si>
   <si>
     <t>VIERDE_KLASSE_B</t>
@@ -1232,8 +1229,11 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{00000000-000C-0000-FFFF-FFFF11000000}" name="TWEEDEKLE11121314151719" displayName="TWEEDEKLE11121314151719" ref="AD1:AD22" totalsRowShown="0">
-  <autoFilter ref="AD1:AD22" xr:uid="{00000000-0009-0000-0100-000012000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{00000000-000C-0000-FFFF-FFFF11000000}" name="TWEEDEKLE11121314151719" displayName="TWEEDEKLE11121314151719" ref="AD1:AD23" totalsRowShown="0">
+  <autoFilter ref="AD1:AD23" xr:uid="{00000000-0009-0000-0100-000012000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="AD2:AD23">
+    <sortCondition ref="AD4:AD23"/>
+  </sortState>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-1100-000001000000}" name="VIERDE KLASSE G"/>
   </tableColumns>
@@ -7673,14 +7673,24 @@
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="F131:H131"/>
-    <mergeCell ref="I131:K131"/>
-    <mergeCell ref="F79:H79"/>
-    <mergeCell ref="I79:K79"/>
-    <mergeCell ref="F92:H92"/>
-    <mergeCell ref="I92:K92"/>
-    <mergeCell ref="F105:H105"/>
-    <mergeCell ref="I105:K105"/>
+    <mergeCell ref="F235:H235"/>
+    <mergeCell ref="I235:K235"/>
+    <mergeCell ref="F248:H248"/>
+    <mergeCell ref="I248:K248"/>
+    <mergeCell ref="F261:H261"/>
+    <mergeCell ref="I261:K261"/>
+    <mergeCell ref="F196:H196"/>
+    <mergeCell ref="I196:K196"/>
+    <mergeCell ref="F209:H209"/>
+    <mergeCell ref="I209:K209"/>
+    <mergeCell ref="F222:H222"/>
+    <mergeCell ref="I222:K222"/>
+    <mergeCell ref="F157:H157"/>
+    <mergeCell ref="I157:K157"/>
+    <mergeCell ref="F170:H170"/>
+    <mergeCell ref="I170:K170"/>
+    <mergeCell ref="F183:H183"/>
+    <mergeCell ref="I183:K183"/>
     <mergeCell ref="F144:H144"/>
     <mergeCell ref="I144:K144"/>
     <mergeCell ref="F1:H1"/>
@@ -7697,24 +7707,14 @@
     <mergeCell ref="I66:K66"/>
     <mergeCell ref="F118:H118"/>
     <mergeCell ref="I118:K118"/>
-    <mergeCell ref="F157:H157"/>
-    <mergeCell ref="I157:K157"/>
-    <mergeCell ref="F170:H170"/>
-    <mergeCell ref="I170:K170"/>
-    <mergeCell ref="F183:H183"/>
-    <mergeCell ref="I183:K183"/>
-    <mergeCell ref="F196:H196"/>
-    <mergeCell ref="I196:K196"/>
-    <mergeCell ref="F209:H209"/>
-    <mergeCell ref="I209:K209"/>
-    <mergeCell ref="F222:H222"/>
-    <mergeCell ref="I222:K222"/>
-    <mergeCell ref="F235:H235"/>
-    <mergeCell ref="I235:K235"/>
-    <mergeCell ref="F248:H248"/>
-    <mergeCell ref="I248:K248"/>
-    <mergeCell ref="F261:H261"/>
-    <mergeCell ref="I261:K261"/>
+    <mergeCell ref="F131:H131"/>
+    <mergeCell ref="I131:K131"/>
+    <mergeCell ref="F79:H79"/>
+    <mergeCell ref="I79:K79"/>
+    <mergeCell ref="F92:H92"/>
+    <mergeCell ref="I92:K92"/>
+    <mergeCell ref="F105:H105"/>
+    <mergeCell ref="I105:K105"/>
   </mergeCells>
   <dataValidations count="24">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1 B131 B27 B40 B53 B66 B79 B92 B105 B118 B14 B144 B157 B170 B183 B196 B209 B222 B235 B248 B261" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -7933,7 +7933,7 @@
       </c>
       <c r="B2" s="1"/>
       <c r="D2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="BF2" t="s">
         <v>7</v>
@@ -7983,7 +7983,7 @@
         <v>42</v>
       </c>
       <c r="AD3" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="AF3" t="s">
         <v>44</v>
@@ -8036,7 +8036,7 @@
         <v>57</v>
       </c>
       <c r="P4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="R4" t="s">
         <v>58</v>
@@ -8057,7 +8057,7 @@
         <v>63</v>
       </c>
       <c r="AD4" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="AF4" t="s">
         <v>65</v>
@@ -8131,10 +8131,10 @@
         <v>85</v>
       </c>
       <c r="AD5" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="AF5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AH5" t="s">
         <v>87</v>
@@ -8205,7 +8205,7 @@
         <v>106</v>
       </c>
       <c r="AD6" t="s">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="AF6" t="s">
         <v>108</v>
@@ -8276,10 +8276,10 @@
         <v>127</v>
       </c>
       <c r="AB7" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AD7" t="s">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="AF7" t="s">
         <v>129</v>
@@ -8353,7 +8353,7 @@
         <v>149</v>
       </c>
       <c r="AD8" t="s">
-        <v>150</v>
+        <v>307</v>
       </c>
       <c r="AF8" t="s">
         <v>151</v>
@@ -8427,7 +8427,7 @@
         <v>171</v>
       </c>
       <c r="AD9" t="s">
-        <v>172</v>
+        <v>128</v>
       </c>
       <c r="AF9" t="s">
         <v>173</v>
@@ -8501,7 +8501,7 @@
         <v>192</v>
       </c>
       <c r="AD10" t="s">
-        <v>193</v>
+        <v>150</v>
       </c>
       <c r="AF10" t="s">
         <v>194</v>
@@ -8525,13 +8525,13 @@
         <v>200</v>
       </c>
       <c r="AT10" t="s">
-        <v>201</v>
+        <v>232</v>
       </c>
       <c r="BF10" t="s">
         <v>15</v>
       </c>
       <c r="BG10" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11" spans="1:59" x14ac:dyDescent="0.25">
@@ -8539,73 +8539,73 @@
         <v>15</v>
       </c>
       <c r="F11" t="s">
+        <v>202</v>
+      </c>
+      <c r="H11" t="s">
         <v>203</v>
       </c>
-      <c r="H11" t="s">
+      <c r="J11" t="s">
         <v>204</v>
       </c>
-      <c r="J11" t="s">
+      <c r="L11" t="s">
         <v>205</v>
       </c>
-      <c r="L11" t="s">
+      <c r="N11" t="s">
         <v>206</v>
       </c>
-      <c r="N11" t="s">
+      <c r="P11" t="s">
         <v>207</v>
       </c>
-      <c r="P11" t="s">
+      <c r="R11" t="s">
         <v>208</v>
       </c>
-      <c r="R11" t="s">
+      <c r="T11" t="s">
         <v>209</v>
       </c>
-      <c r="T11" t="s">
+      <c r="V11" t="s">
         <v>210</v>
       </c>
-      <c r="V11" t="s">
+      <c r="X11" t="s">
         <v>211</v>
       </c>
-      <c r="X11" t="s">
+      <c r="Z11" t="s">
         <v>212</v>
       </c>
-      <c r="Z11" t="s">
+      <c r="AB11" t="s">
         <v>213</v>
       </c>
-      <c r="AB11" t="s">
+      <c r="AD11" t="s">
+        <v>172</v>
+      </c>
+      <c r="AF11" t="s">
         <v>214</v>
       </c>
-      <c r="AD11" t="s">
-        <v>308</v>
-      </c>
-      <c r="AF11" t="s">
+      <c r="AH11" t="s">
         <v>215</v>
       </c>
-      <c r="AH11" t="s">
+      <c r="AJ11" t="s">
         <v>216</v>
       </c>
-      <c r="AJ11" t="s">
+      <c r="AL11" t="s">
         <v>217</v>
       </c>
-      <c r="AL11" t="s">
+      <c r="AN11" t="s">
         <v>218</v>
       </c>
-      <c r="AN11" t="s">
+      <c r="AP11" t="s">
         <v>219</v>
       </c>
-      <c r="AP11" t="s">
+      <c r="AR11" t="s">
         <v>220</v>
       </c>
-      <c r="AR11" t="s">
+      <c r="AT11" t="s">
         <v>221</v>
-      </c>
-      <c r="AT11" t="s">
-        <v>222</v>
       </c>
       <c r="BF11" t="s">
         <v>16</v>
       </c>
       <c r="BG11" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="12" spans="1:59" x14ac:dyDescent="0.25">
@@ -8613,73 +8613,73 @@
         <v>16</v>
       </c>
       <c r="F12" t="s">
+        <v>223</v>
+      </c>
+      <c r="H12" t="s">
+        <v>220</v>
+      </c>
+      <c r="J12" t="s">
         <v>224</v>
       </c>
-      <c r="H12" t="s">
-        <v>221</v>
-      </c>
-      <c r="J12" t="s">
+      <c r="L12" t="s">
+        <v>311</v>
+      </c>
+      <c r="N12" t="s">
         <v>225</v>
       </c>
-      <c r="L12" t="s">
-        <v>312</v>
-      </c>
-      <c r="N12" t="s">
+      <c r="P12" t="s">
         <v>226</v>
       </c>
-      <c r="P12" t="s">
+      <c r="R12" t="s">
         <v>227</v>
       </c>
-      <c r="R12" t="s">
+      <c r="T12" t="s">
         <v>228</v>
       </c>
-      <c r="T12" t="s">
+      <c r="V12" t="s">
         <v>229</v>
       </c>
-      <c r="V12" t="s">
+      <c r="X12" t="s">
         <v>230</v>
       </c>
-      <c r="X12" t="s">
+      <c r="Z12" t="s">
         <v>231</v>
       </c>
-      <c r="Z12" t="s">
+      <c r="AB12" t="s">
         <v>232</v>
       </c>
-      <c r="AB12" t="s">
-        <v>233</v>
-      </c>
       <c r="AD12" t="s">
+        <v>193</v>
+      </c>
+      <c r="AF12" t="s">
         <v>234</v>
       </c>
-      <c r="AF12" t="s">
+      <c r="AH12" t="s">
         <v>235</v>
       </c>
-      <c r="AH12" t="s">
+      <c r="AJ12" t="s">
         <v>236</v>
       </c>
-      <c r="AJ12" t="s">
+      <c r="AL12" t="s">
         <v>237</v>
       </c>
-      <c r="AL12" t="s">
+      <c r="AN12" t="s">
         <v>238</v>
       </c>
-      <c r="AN12" t="s">
+      <c r="AP12" t="s">
         <v>239</v>
-      </c>
-      <c r="AP12" t="s">
-        <v>240</v>
       </c>
       <c r="AR12" t="s">
         <v>103</v>
       </c>
       <c r="AT12" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="BF12" t="s">
         <v>17</v>
       </c>
       <c r="BG12" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="13" spans="1:59" x14ac:dyDescent="0.25">
@@ -8687,73 +8687,73 @@
         <v>17</v>
       </c>
       <c r="F13" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H13" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J13" t="s">
         <v>200</v>
       </c>
       <c r="L13" t="s">
+        <v>243</v>
+      </c>
+      <c r="N13" t="s">
         <v>244</v>
       </c>
-      <c r="N13" t="s">
+      <c r="P13" t="s">
         <v>245</v>
       </c>
-      <c r="P13" t="s">
+      <c r="R13" t="s">
         <v>246</v>
       </c>
-      <c r="R13" t="s">
+      <c r="T13" t="s">
         <v>247</v>
       </c>
-      <c r="T13" t="s">
+      <c r="V13" t="s">
         <v>248</v>
       </c>
-      <c r="V13" t="s">
+      <c r="X13" t="s">
         <v>249</v>
       </c>
-      <c r="X13" t="s">
+      <c r="Z13" t="s">
         <v>250</v>
       </c>
-      <c r="Z13" t="s">
+      <c r="AB13" t="s">
         <v>251</v>
       </c>
-      <c r="AB13" t="s">
-        <v>252</v>
-      </c>
       <c r="AD13" t="s">
+        <v>233</v>
+      </c>
+      <c r="AF13" t="s">
         <v>253</v>
       </c>
-      <c r="AF13" t="s">
+      <c r="AH13" t="s">
         <v>254</v>
       </c>
-      <c r="AH13" t="s">
+      <c r="AJ13" t="s">
         <v>255</v>
       </c>
-      <c r="AJ13" t="s">
+      <c r="AL13" t="s">
         <v>256</v>
       </c>
-      <c r="AL13" t="s">
+      <c r="AN13" t="s">
         <v>257</v>
       </c>
-      <c r="AN13" t="s">
+      <c r="AP13" t="s">
         <v>258</v>
       </c>
-      <c r="AP13" t="s">
+      <c r="AR13" t="s">
         <v>259</v>
       </c>
-      <c r="AR13" t="s">
+      <c r="AT13" t="s">
         <v>260</v>
-      </c>
-      <c r="AT13" t="s">
-        <v>261</v>
       </c>
       <c r="BF13" t="s">
         <v>18</v>
       </c>
       <c r="BG13" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="14" spans="1:59" x14ac:dyDescent="0.25">
@@ -8761,64 +8761,64 @@
         <v>18</v>
       </c>
       <c r="F14" t="s">
+        <v>262</v>
+      </c>
+      <c r="H14" t="s">
         <v>263</v>
       </c>
-      <c r="H14" t="s">
+      <c r="J14" t="s">
         <v>264</v>
       </c>
-      <c r="J14" t="s">
+      <c r="L14" t="s">
         <v>265</v>
       </c>
-      <c r="L14" t="s">
+      <c r="N14" t="s">
         <v>266</v>
       </c>
-      <c r="N14" t="s">
+      <c r="P14" t="s">
         <v>267</v>
       </c>
-      <c r="P14" t="s">
+      <c r="R14" t="s">
         <v>268</v>
       </c>
-      <c r="R14" t="s">
+      <c r="T14" t="s">
         <v>269</v>
       </c>
-      <c r="T14" t="s">
+      <c r="X14" t="s">
         <v>270</v>
       </c>
-      <c r="X14" t="s">
+      <c r="AB14" t="s">
         <v>271</v>
       </c>
-      <c r="AB14" t="s">
+      <c r="AD14" t="s">
         <v>272</v>
       </c>
-      <c r="AD14" t="s">
+      <c r="AF14" t="s">
         <v>273</v>
       </c>
-      <c r="AF14" t="s">
+      <c r="AH14" t="s">
         <v>274</v>
       </c>
-      <c r="AH14" t="s">
+      <c r="AL14" t="s">
+        <v>309</v>
+      </c>
+      <c r="AN14" t="s">
         <v>275</v>
       </c>
-      <c r="AL14" t="s">
-        <v>310</v>
-      </c>
-      <c r="AN14" t="s">
+      <c r="AP14" t="s">
         <v>276</v>
       </c>
-      <c r="AP14" t="s">
+      <c r="AR14" t="s">
         <v>277</v>
       </c>
-      <c r="AR14" t="s">
+      <c r="AT14" t="s">
         <v>278</v>
-      </c>
-      <c r="AT14" t="s">
-        <v>279</v>
       </c>
       <c r="BF14" t="s">
         <v>19</v>
       </c>
       <c r="BG14" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:59" x14ac:dyDescent="0.25">
@@ -8826,31 +8826,31 @@
         <v>19</v>
       </c>
       <c r="F15" t="s">
+        <v>280</v>
+      </c>
+      <c r="H15" t="s">
         <v>281</v>
       </c>
-      <c r="H15" t="s">
+      <c r="J15" t="s">
         <v>282</v>
       </c>
-      <c r="J15" t="s">
+      <c r="L15" t="s">
         <v>283</v>
       </c>
-      <c r="L15" t="s">
+      <c r="N15" t="s">
         <v>284</v>
       </c>
-      <c r="N15" t="s">
+      <c r="P15" t="s">
         <v>285</v>
       </c>
-      <c r="P15" t="s">
+      <c r="R15" t="s">
         <v>286</v>
-      </c>
-      <c r="R15" t="s">
-        <v>287</v>
       </c>
       <c r="BF15" t="s">
         <v>20</v>
       </c>
       <c r="BG15" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="16" spans="1:59" x14ac:dyDescent="0.25">
@@ -8858,28 +8858,28 @@
         <v>20</v>
       </c>
       <c r="F16" t="s">
+        <v>288</v>
+      </c>
+      <c r="H16" t="s">
         <v>289</v>
       </c>
-      <c r="H16" t="s">
+      <c r="J16" t="s">
         <v>290</v>
       </c>
-      <c r="J16" t="s">
+      <c r="L16" t="s">
         <v>291</v>
       </c>
-      <c r="L16" t="s">
+      <c r="N16" t="s">
         <v>292</v>
       </c>
-      <c r="N16" t="s">
+      <c r="R16" t="s">
         <v>293</v>
-      </c>
-      <c r="R16" t="s">
-        <v>294</v>
       </c>
       <c r="BF16" t="s">
         <v>21</v>
       </c>
       <c r="BG16" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="17" spans="4:59" x14ac:dyDescent="0.25">
@@ -8887,16 +8887,16 @@
         <v>21</v>
       </c>
       <c r="F17" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="BF17" t="s">
         <v>22</v>
       </c>
       <c r="BG17" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="18" spans="4:59" x14ac:dyDescent="0.25">
@@ -8904,16 +8904,16 @@
         <v>22</v>
       </c>
       <c r="F18" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H18" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="BF18" t="s">
         <v>23</v>
       </c>
       <c r="BG18" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="19" spans="4:59" x14ac:dyDescent="0.25">
@@ -8921,13 +8921,13 @@
         <v>23</v>
       </c>
       <c r="F19" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="BF19" t="s">
         <v>24</v>
       </c>
       <c r="BG19" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="20" spans="4:59" x14ac:dyDescent="0.25">
@@ -8935,13 +8935,13 @@
         <v>24</v>
       </c>
       <c r="F20" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="BF20" t="s">
         <v>25</v>
       </c>
       <c r="BG20" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="21" spans="4:59" x14ac:dyDescent="0.25">
@@ -8952,7 +8952,7 @@
         <v>26</v>
       </c>
       <c r="BG21" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="22" spans="4:59" x14ac:dyDescent="0.25">
@@ -8963,7 +8963,7 @@
         <v>27</v>
       </c>
       <c r="BG22" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="23" spans="4:59" x14ac:dyDescent="0.25">

--- a/static/docs/AMA_uitslagen amateuvoetbal 2025-2026 definitief.xlsx
+++ b/static/docs/AMA_uitslagen amateuvoetbal 2025-2026 definitief.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mediahuis-my.sharepoint.com/personal/torsten_faruhn_delimburger_nl/Documents/Torsten/CUE Print/amateur- en regiosport nieuwe stijl/uitslagendienst/amateurvoetbal/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="102" documentId="8_{F6EDDE6E-FDD8-41E1-97DF-2A01485E9FFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3EBEF0B9-02C7-4F88-AD7C-181575E213BE}"/>
+  <xr:revisionPtr revIDLastSave="112" documentId="8_{F6EDDE6E-FDD8-41E1-97DF-2A01485E9FFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1AC8C493-21C7-4729-A1CB-AF004EDF4EB9}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INVOER" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="863" uniqueCount="314">
   <si>
     <t>KLASSE</t>
   </si>
@@ -375,9 +375,6 @@
     <t>Partij</t>
   </si>
   <si>
-    <t>Kakterse Boys</t>
-  </si>
-  <si>
     <t>FC RIA</t>
   </si>
   <si>
@@ -825,9 +822,6 @@
     <t>Holthees-Smakt</t>
   </si>
   <si>
-    <t>DVC'19</t>
-  </si>
-  <si>
     <t>FSG</t>
   </si>
   <si>
@@ -985,6 +979,15 @@
   </si>
   <si>
     <t>OJC Rosmalen</t>
+  </si>
+  <si>
+    <t>KSV Horn</t>
+  </si>
+  <si>
+    <t>Kakertse Boys</t>
+  </si>
+  <si>
+    <t>DVC'16</t>
   </si>
 </sst>
 </file>
@@ -7673,24 +7676,14 @@
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="F235:H235"/>
-    <mergeCell ref="I235:K235"/>
-    <mergeCell ref="F248:H248"/>
-    <mergeCell ref="I248:K248"/>
-    <mergeCell ref="F261:H261"/>
-    <mergeCell ref="I261:K261"/>
-    <mergeCell ref="F196:H196"/>
-    <mergeCell ref="I196:K196"/>
-    <mergeCell ref="F209:H209"/>
-    <mergeCell ref="I209:K209"/>
-    <mergeCell ref="F222:H222"/>
-    <mergeCell ref="I222:K222"/>
-    <mergeCell ref="F157:H157"/>
-    <mergeCell ref="I157:K157"/>
-    <mergeCell ref="F170:H170"/>
-    <mergeCell ref="I170:K170"/>
-    <mergeCell ref="F183:H183"/>
-    <mergeCell ref="I183:K183"/>
+    <mergeCell ref="F131:H131"/>
+    <mergeCell ref="I131:K131"/>
+    <mergeCell ref="F79:H79"/>
+    <mergeCell ref="I79:K79"/>
+    <mergeCell ref="F92:H92"/>
+    <mergeCell ref="I92:K92"/>
+    <mergeCell ref="F105:H105"/>
+    <mergeCell ref="I105:K105"/>
     <mergeCell ref="F144:H144"/>
     <mergeCell ref="I144:K144"/>
     <mergeCell ref="F1:H1"/>
@@ -7707,14 +7700,24 @@
     <mergeCell ref="I66:K66"/>
     <mergeCell ref="F118:H118"/>
     <mergeCell ref="I118:K118"/>
-    <mergeCell ref="F131:H131"/>
-    <mergeCell ref="I131:K131"/>
-    <mergeCell ref="F79:H79"/>
-    <mergeCell ref="I79:K79"/>
-    <mergeCell ref="F92:H92"/>
-    <mergeCell ref="I92:K92"/>
-    <mergeCell ref="F105:H105"/>
-    <mergeCell ref="I105:K105"/>
+    <mergeCell ref="F157:H157"/>
+    <mergeCell ref="I157:K157"/>
+    <mergeCell ref="F170:H170"/>
+    <mergeCell ref="I170:K170"/>
+    <mergeCell ref="F183:H183"/>
+    <mergeCell ref="I183:K183"/>
+    <mergeCell ref="F196:H196"/>
+    <mergeCell ref="I196:K196"/>
+    <mergeCell ref="F209:H209"/>
+    <mergeCell ref="I209:K209"/>
+    <mergeCell ref="F222:H222"/>
+    <mergeCell ref="I222:K222"/>
+    <mergeCell ref="F235:H235"/>
+    <mergeCell ref="I235:K235"/>
+    <mergeCell ref="F248:H248"/>
+    <mergeCell ref="I248:K248"/>
+    <mergeCell ref="F261:H261"/>
+    <mergeCell ref="I261:K261"/>
   </mergeCells>
   <dataValidations count="24">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1 B131 B27 B40 B53 B66 B79 B92 B105 B118 B14 B144 B157 B170 B183 B196 B209 B222 B235 B248 B261" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -7933,7 +7936,7 @@
       </c>
       <c r="B2" s="1"/>
       <c r="D2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="BF2" t="s">
         <v>7</v>
@@ -7983,7 +7986,7 @@
         <v>42</v>
       </c>
       <c r="AD3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AF3" t="s">
         <v>44</v>
@@ -8036,7 +8039,7 @@
         <v>57</v>
       </c>
       <c r="P4" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="R4" t="s">
         <v>58</v>
@@ -8134,7 +8137,7 @@
         <v>64</v>
       </c>
       <c r="AF5" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="AH5" t="s">
         <v>87</v>
@@ -8211,31 +8214,31 @@
         <v>108</v>
       </c>
       <c r="AH6" t="s">
+        <v>312</v>
+      </c>
+      <c r="AJ6" t="s">
         <v>109</v>
       </c>
-      <c r="AJ6" t="s">
+      <c r="AL6" t="s">
         <v>110</v>
       </c>
-      <c r="AL6" t="s">
+      <c r="AN6" t="s">
         <v>111</v>
       </c>
-      <c r="AN6" t="s">
+      <c r="AP6" t="s">
         <v>112</v>
       </c>
-      <c r="AP6" t="s">
+      <c r="AR6" t="s">
         <v>113</v>
       </c>
-      <c r="AR6" t="s">
+      <c r="AT6" t="s">
         <v>114</v>
-      </c>
-      <c r="AT6" t="s">
-        <v>115</v>
       </c>
       <c r="BF6" t="s">
         <v>11</v>
       </c>
       <c r="BG6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:59" x14ac:dyDescent="0.25">
@@ -8243,73 +8246,73 @@
         <v>11</v>
       </c>
       <c r="F7" t="s">
+        <v>116</v>
+      </c>
+      <c r="H7" t="s">
         <v>117</v>
       </c>
-      <c r="H7" t="s">
+      <c r="J7" t="s">
         <v>118</v>
       </c>
-      <c r="J7" t="s">
+      <c r="L7" t="s">
         <v>119</v>
       </c>
-      <c r="L7" t="s">
+      <c r="N7" t="s">
         <v>120</v>
       </c>
-      <c r="N7" t="s">
+      <c r="P7" t="s">
         <v>121</v>
       </c>
-      <c r="P7" t="s">
+      <c r="R7" t="s">
         <v>122</v>
       </c>
-      <c r="R7" t="s">
+      <c r="T7" t="s">
         <v>123</v>
       </c>
-      <c r="T7" t="s">
+      <c r="V7" t="s">
         <v>124</v>
       </c>
-      <c r="V7" t="s">
+      <c r="X7" t="s">
         <v>125</v>
       </c>
-      <c r="X7" t="s">
+      <c r="Z7" t="s">
         <v>126</v>
       </c>
-      <c r="Z7" t="s">
-        <v>127</v>
-      </c>
       <c r="AB7" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="AD7" t="s">
         <v>107</v>
       </c>
       <c r="AF7" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH7" t="s">
         <v>129</v>
       </c>
-      <c r="AH7" t="s">
+      <c r="AJ7" t="s">
         <v>130</v>
       </c>
-      <c r="AJ7" t="s">
+      <c r="AL7" t="s">
         <v>131</v>
       </c>
-      <c r="AL7" t="s">
+      <c r="AN7" t="s">
         <v>132</v>
       </c>
-      <c r="AN7" t="s">
+      <c r="AP7" t="s">
         <v>133</v>
       </c>
-      <c r="AP7" t="s">
+      <c r="AR7" t="s">
         <v>134</v>
       </c>
-      <c r="AR7" t="s">
+      <c r="AT7" t="s">
         <v>135</v>
-      </c>
-      <c r="AT7" t="s">
-        <v>136</v>
       </c>
       <c r="BF7" t="s">
         <v>12</v>
       </c>
       <c r="BG7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="1:59" x14ac:dyDescent="0.25">
@@ -8317,73 +8320,73 @@
         <v>12</v>
       </c>
       <c r="F8" t="s">
+        <v>137</v>
+      </c>
+      <c r="H8" t="s">
         <v>138</v>
       </c>
-      <c r="H8" t="s">
+      <c r="J8" t="s">
         <v>139</v>
       </c>
-      <c r="J8" t="s">
+      <c r="L8" t="s">
         <v>140</v>
       </c>
-      <c r="L8" t="s">
+      <c r="N8" t="s">
         <v>141</v>
       </c>
-      <c r="N8" t="s">
+      <c r="P8" t="s">
         <v>142</v>
       </c>
-      <c r="P8" t="s">
+      <c r="R8" t="s">
         <v>143</v>
       </c>
-      <c r="R8" t="s">
+      <c r="T8" t="s">
         <v>144</v>
       </c>
-      <c r="T8" t="s">
+      <c r="V8" t="s">
         <v>145</v>
       </c>
-      <c r="V8" t="s">
+      <c r="X8" t="s">
         <v>146</v>
       </c>
-      <c r="X8" t="s">
-        <v>147</v>
-      </c>
       <c r="Z8" t="s">
+        <v>311</v>
+      </c>
+      <c r="AB8" t="s">
         <v>148</v>
       </c>
-      <c r="AB8" t="s">
-        <v>149</v>
-      </c>
       <c r="AD8" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="AF8" t="s">
+        <v>150</v>
+      </c>
+      <c r="AH8" t="s">
         <v>151</v>
       </c>
-      <c r="AH8" t="s">
+      <c r="AJ8" t="s">
         <v>152</v>
       </c>
-      <c r="AJ8" t="s">
+      <c r="AL8" t="s">
         <v>153</v>
       </c>
-      <c r="AL8" t="s">
+      <c r="AN8" t="s">
         <v>154</v>
       </c>
-      <c r="AN8" t="s">
+      <c r="AP8" t="s">
         <v>155</v>
       </c>
-      <c r="AP8" t="s">
+      <c r="AR8" t="s">
         <v>156</v>
       </c>
-      <c r="AR8" t="s">
+      <c r="AT8" t="s">
         <v>157</v>
-      </c>
-      <c r="AT8" t="s">
-        <v>158</v>
       </c>
       <c r="BF8" t="s">
         <v>13</v>
       </c>
       <c r="BG8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9" spans="1:59" x14ac:dyDescent="0.25">
@@ -8391,67 +8394,67 @@
         <v>13</v>
       </c>
       <c r="F9" t="s">
+        <v>159</v>
+      </c>
+      <c r="H9" t="s">
         <v>160</v>
       </c>
-      <c r="H9" t="s">
+      <c r="J9" t="s">
         <v>161</v>
       </c>
-      <c r="J9" t="s">
+      <c r="L9" t="s">
         <v>162</v>
       </c>
-      <c r="L9" t="s">
+      <c r="N9" t="s">
         <v>163</v>
       </c>
-      <c r="N9" t="s">
+      <c r="P9" t="s">
         <v>164</v>
       </c>
-      <c r="P9" t="s">
+      <c r="R9" t="s">
         <v>165</v>
       </c>
-      <c r="R9" t="s">
+      <c r="T9" t="s">
         <v>166</v>
       </c>
-      <c r="T9" t="s">
+      <c r="V9" t="s">
         <v>167</v>
       </c>
-      <c r="V9" t="s">
+      <c r="X9" t="s">
         <v>168</v>
       </c>
-      <c r="X9" t="s">
-        <v>169</v>
-      </c>
       <c r="Z9" t="s">
+        <v>147</v>
+      </c>
+      <c r="AB9" t="s">
         <v>170</v>
       </c>
-      <c r="AB9" t="s">
-        <v>171</v>
-      </c>
       <c r="AD9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AF9" t="s">
+        <v>172</v>
+      </c>
+      <c r="AH9" t="s">
         <v>173</v>
       </c>
-      <c r="AH9" t="s">
+      <c r="AJ9" t="s">
         <v>174</v>
       </c>
-      <c r="AJ9" t="s">
+      <c r="AL9" t="s">
         <v>175</v>
       </c>
-      <c r="AL9" t="s">
+      <c r="AN9" t="s">
         <v>176</v>
       </c>
-      <c r="AN9" t="s">
+      <c r="AP9" t="s">
         <v>177</v>
       </c>
-      <c r="AP9" t="s">
+      <c r="AR9" t="s">
         <v>178</v>
       </c>
-      <c r="AR9" t="s">
+      <c r="AT9" t="s">
         <v>179</v>
-      </c>
-      <c r="AT9" t="s">
-        <v>180</v>
       </c>
       <c r="BF9" t="s">
         <v>14</v>
@@ -8465,73 +8468,73 @@
         <v>14</v>
       </c>
       <c r="F10" t="s">
+        <v>180</v>
+      </c>
+      <c r="H10" t="s">
         <v>181</v>
       </c>
-      <c r="H10" t="s">
+      <c r="J10" t="s">
         <v>182</v>
       </c>
-      <c r="J10" t="s">
+      <c r="L10" t="s">
         <v>183</v>
       </c>
-      <c r="L10" t="s">
+      <c r="N10" t="s">
         <v>184</v>
       </c>
-      <c r="N10" t="s">
+      <c r="P10" t="s">
         <v>185</v>
       </c>
-      <c r="P10" t="s">
+      <c r="R10" t="s">
         <v>186</v>
       </c>
-      <c r="R10" t="s">
+      <c r="T10" t="s">
         <v>187</v>
       </c>
-      <c r="T10" t="s">
+      <c r="V10" t="s">
         <v>188</v>
       </c>
-      <c r="V10" t="s">
+      <c r="X10" t="s">
         <v>189</v>
       </c>
-      <c r="X10" t="s">
-        <v>190</v>
-      </c>
       <c r="Z10" t="s">
+        <v>169</v>
+      </c>
+      <c r="AB10" t="s">
         <v>191</v>
       </c>
-      <c r="AB10" t="s">
-        <v>192</v>
-      </c>
       <c r="AD10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AF10" t="s">
+        <v>193</v>
+      </c>
+      <c r="AH10" t="s">
         <v>194</v>
       </c>
-      <c r="AH10" t="s">
+      <c r="AJ10" t="s">
         <v>195</v>
       </c>
-      <c r="AJ10" t="s">
+      <c r="AL10" t="s">
         <v>196</v>
       </c>
-      <c r="AL10" t="s">
+      <c r="AN10" t="s">
         <v>197</v>
       </c>
-      <c r="AN10" t="s">
+      <c r="AP10" t="s">
         <v>198</v>
       </c>
-      <c r="AP10" t="s">
+      <c r="AR10" t="s">
         <v>199</v>
       </c>
-      <c r="AR10" t="s">
-        <v>200</v>
-      </c>
       <c r="AT10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="BF10" t="s">
         <v>15</v>
       </c>
       <c r="BG10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11" spans="1:59" x14ac:dyDescent="0.25">
@@ -8539,73 +8542,73 @@
         <v>15</v>
       </c>
       <c r="F11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H11" t="s">
         <v>202</v>
       </c>
-      <c r="H11" t="s">
+      <c r="J11" t="s">
         <v>203</v>
       </c>
-      <c r="J11" t="s">
+      <c r="L11" t="s">
         <v>204</v>
       </c>
-      <c r="L11" t="s">
+      <c r="N11" t="s">
         <v>205</v>
       </c>
-      <c r="N11" t="s">
+      <c r="P11" t="s">
         <v>206</v>
       </c>
-      <c r="P11" t="s">
+      <c r="R11" t="s">
         <v>207</v>
       </c>
-      <c r="R11" t="s">
+      <c r="T11" t="s">
         <v>208</v>
       </c>
-      <c r="T11" t="s">
+      <c r="V11" t="s">
         <v>209</v>
       </c>
-      <c r="V11" t="s">
+      <c r="X11" t="s">
         <v>210</v>
       </c>
-      <c r="X11" t="s">
-        <v>211</v>
-      </c>
       <c r="Z11" t="s">
+        <v>190</v>
+      </c>
+      <c r="AB11" t="s">
         <v>212</v>
       </c>
-      <c r="AB11" t="s">
+      <c r="AD11" t="s">
+        <v>171</v>
+      </c>
+      <c r="AF11" t="s">
         <v>213</v>
       </c>
-      <c r="AD11" t="s">
-        <v>172</v>
-      </c>
-      <c r="AF11" t="s">
+      <c r="AH11" t="s">
         <v>214</v>
       </c>
-      <c r="AH11" t="s">
+      <c r="AJ11" t="s">
         <v>215</v>
       </c>
-      <c r="AJ11" t="s">
+      <c r="AL11" t="s">
         <v>216</v>
       </c>
-      <c r="AL11" t="s">
+      <c r="AN11" t="s">
         <v>217</v>
       </c>
-      <c r="AN11" t="s">
+      <c r="AP11" t="s">
         <v>218</v>
       </c>
-      <c r="AP11" t="s">
+      <c r="AR11" t="s">
         <v>219</v>
       </c>
-      <c r="AR11" t="s">
+      <c r="AT11" t="s">
         <v>220</v>
-      </c>
-      <c r="AT11" t="s">
-        <v>221</v>
       </c>
       <c r="BF11" t="s">
         <v>16</v>
       </c>
       <c r="BG11" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="12" spans="1:59" x14ac:dyDescent="0.25">
@@ -8613,73 +8616,73 @@
         <v>16</v>
       </c>
       <c r="F12" t="s">
+        <v>222</v>
+      </c>
+      <c r="H12" t="s">
+        <v>219</v>
+      </c>
+      <c r="J12" t="s">
         <v>223</v>
       </c>
-      <c r="H12" t="s">
-        <v>220</v>
-      </c>
-      <c r="J12" t="s">
+      <c r="L12" t="s">
+        <v>309</v>
+      </c>
+      <c r="N12" t="s">
         <v>224</v>
       </c>
-      <c r="L12" t="s">
-        <v>311</v>
-      </c>
-      <c r="N12" t="s">
+      <c r="P12" t="s">
         <v>225</v>
       </c>
-      <c r="P12" t="s">
+      <c r="R12" t="s">
         <v>226</v>
       </c>
-      <c r="R12" t="s">
+      <c r="T12" t="s">
         <v>227</v>
       </c>
-      <c r="T12" t="s">
+      <c r="V12" t="s">
         <v>228</v>
       </c>
-      <c r="V12" t="s">
+      <c r="X12" t="s">
         <v>229</v>
       </c>
-      <c r="X12" t="s">
-        <v>230</v>
-      </c>
       <c r="Z12" t="s">
+        <v>211</v>
+      </c>
+      <c r="AB12" t="s">
         <v>231</v>
       </c>
-      <c r="AB12" t="s">
-        <v>232</v>
-      </c>
       <c r="AD12" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AF12" t="s">
+        <v>233</v>
+      </c>
+      <c r="AH12" t="s">
         <v>234</v>
       </c>
-      <c r="AH12" t="s">
+      <c r="AJ12" t="s">
         <v>235</v>
       </c>
-      <c r="AJ12" t="s">
+      <c r="AL12" t="s">
         <v>236</v>
       </c>
-      <c r="AL12" t="s">
+      <c r="AN12" t="s">
         <v>237</v>
       </c>
-      <c r="AN12" t="s">
+      <c r="AP12" t="s">
         <v>238</v>
-      </c>
-      <c r="AP12" t="s">
-        <v>239</v>
       </c>
       <c r="AR12" t="s">
         <v>103</v>
       </c>
       <c r="AT12" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="BF12" t="s">
         <v>17</v>
       </c>
       <c r="BG12" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="13" spans="1:59" x14ac:dyDescent="0.25">
@@ -8687,73 +8690,73 @@
         <v>17</v>
       </c>
       <c r="F13" t="s">
+        <v>241</v>
+      </c>
+      <c r="H13" t="s">
+        <v>310</v>
+      </c>
+      <c r="J13" t="s">
+        <v>199</v>
+      </c>
+      <c r="L13" t="s">
         <v>242</v>
       </c>
-      <c r="H13" t="s">
-        <v>312</v>
-      </c>
-      <c r="J13" t="s">
-        <v>200</v>
-      </c>
-      <c r="L13" t="s">
+      <c r="N13" t="s">
         <v>243</v>
       </c>
-      <c r="N13" t="s">
+      <c r="P13" t="s">
         <v>244</v>
       </c>
-      <c r="P13" t="s">
+      <c r="R13" t="s">
         <v>245</v>
       </c>
-      <c r="R13" t="s">
+      <c r="T13" t="s">
         <v>246</v>
       </c>
-      <c r="T13" t="s">
+      <c r="V13" t="s">
         <v>247</v>
       </c>
-      <c r="V13" t="s">
+      <c r="X13" t="s">
         <v>248</v>
       </c>
-      <c r="X13" t="s">
-        <v>249</v>
-      </c>
       <c r="Z13" t="s">
+        <v>230</v>
+      </c>
+      <c r="AB13" t="s">
         <v>250</v>
       </c>
-      <c r="AB13" t="s">
-        <v>251</v>
-      </c>
       <c r="AD13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AF13" t="s">
+        <v>252</v>
+      </c>
+      <c r="AH13" t="s">
         <v>253</v>
       </c>
-      <c r="AH13" t="s">
+      <c r="AJ13" t="s">
         <v>254</v>
       </c>
-      <c r="AJ13" t="s">
+      <c r="AL13" t="s">
         <v>255</v>
       </c>
-      <c r="AL13" t="s">
+      <c r="AN13" t="s">
         <v>256</v>
       </c>
-      <c r="AN13" t="s">
+      <c r="AP13" t="s">
         <v>257</v>
       </c>
-      <c r="AP13" t="s">
+      <c r="AR13" t="s">
+        <v>313</v>
+      </c>
+      <c r="AT13" t="s">
         <v>258</v>
-      </c>
-      <c r="AR13" t="s">
-        <v>259</v>
-      </c>
-      <c r="AT13" t="s">
-        <v>260</v>
       </c>
       <c r="BF13" t="s">
         <v>18</v>
       </c>
       <c r="BG13" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="14" spans="1:59" x14ac:dyDescent="0.25">
@@ -8761,64 +8764,67 @@
         <v>18</v>
       </c>
       <c r="F14" t="s">
+        <v>260</v>
+      </c>
+      <c r="H14" t="s">
+        <v>261</v>
+      </c>
+      <c r="J14" t="s">
         <v>262</v>
       </c>
-      <c r="H14" t="s">
+      <c r="L14" t="s">
         <v>263</v>
       </c>
-      <c r="J14" t="s">
+      <c r="N14" t="s">
         <v>264</v>
       </c>
-      <c r="L14" t="s">
+      <c r="P14" t="s">
         <v>265</v>
       </c>
-      <c r="N14" t="s">
+      <c r="R14" t="s">
         <v>266</v>
       </c>
-      <c r="P14" t="s">
+      <c r="T14" t="s">
         <v>267</v>
       </c>
-      <c r="R14" t="s">
+      <c r="X14" t="s">
         <v>268</v>
       </c>
-      <c r="T14" t="s">
+      <c r="Z14" t="s">
+        <v>249</v>
+      </c>
+      <c r="AB14" t="s">
         <v>269</v>
       </c>
-      <c r="X14" t="s">
+      <c r="AD14" t="s">
         <v>270</v>
       </c>
-      <c r="AB14" t="s">
+      <c r="AF14" t="s">
         <v>271</v>
       </c>
-      <c r="AD14" t="s">
+      <c r="AH14" t="s">
         <v>272</v>
       </c>
-      <c r="AF14" t="s">
+      <c r="AL14" t="s">
+        <v>307</v>
+      </c>
+      <c r="AN14" t="s">
         <v>273</v>
       </c>
-      <c r="AH14" t="s">
+      <c r="AP14" t="s">
         <v>274</v>
       </c>
-      <c r="AL14" t="s">
-        <v>309</v>
-      </c>
-      <c r="AN14" t="s">
+      <c r="AR14" t="s">
         <v>275</v>
       </c>
-      <c r="AP14" t="s">
+      <c r="AT14" t="s">
         <v>276</v>
-      </c>
-      <c r="AR14" t="s">
-        <v>277</v>
-      </c>
-      <c r="AT14" t="s">
-        <v>278</v>
       </c>
       <c r="BF14" t="s">
         <v>19</v>
       </c>
       <c r="BG14" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:59" x14ac:dyDescent="0.25">
@@ -8826,31 +8832,31 @@
         <v>19</v>
       </c>
       <c r="F15" t="s">
+        <v>278</v>
+      </c>
+      <c r="H15" t="s">
+        <v>279</v>
+      </c>
+      <c r="J15" t="s">
         <v>280</v>
       </c>
-      <c r="H15" t="s">
+      <c r="L15" t="s">
         <v>281</v>
       </c>
-      <c r="J15" t="s">
+      <c r="N15" t="s">
         <v>282</v>
       </c>
-      <c r="L15" t="s">
+      <c r="P15" t="s">
         <v>283</v>
       </c>
-      <c r="N15" t="s">
+      <c r="R15" t="s">
         <v>284</v>
-      </c>
-      <c r="P15" t="s">
-        <v>285</v>
-      </c>
-      <c r="R15" t="s">
-        <v>286</v>
       </c>
       <c r="BF15" t="s">
         <v>20</v>
       </c>
       <c r="BG15" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="16" spans="1:59" x14ac:dyDescent="0.25">
@@ -8858,28 +8864,28 @@
         <v>20</v>
       </c>
       <c r="F16" t="s">
+        <v>286</v>
+      </c>
+      <c r="H16" t="s">
+        <v>287</v>
+      </c>
+      <c r="J16" t="s">
         <v>288</v>
       </c>
-      <c r="H16" t="s">
+      <c r="L16" t="s">
         <v>289</v>
       </c>
-      <c r="J16" t="s">
+      <c r="N16" t="s">
         <v>290</v>
       </c>
-      <c r="L16" t="s">
+      <c r="R16" t="s">
         <v>291</v>
-      </c>
-      <c r="N16" t="s">
-        <v>292</v>
-      </c>
-      <c r="R16" t="s">
-        <v>293</v>
       </c>
       <c r="BF16" t="s">
         <v>21</v>
       </c>
       <c r="BG16" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="17" spans="4:59" x14ac:dyDescent="0.25">
@@ -8887,16 +8893,16 @@
         <v>21</v>
       </c>
       <c r="F17" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="H17" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="BF17" t="s">
         <v>22</v>
       </c>
       <c r="BG17" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="18" spans="4:59" x14ac:dyDescent="0.25">
@@ -8904,16 +8910,16 @@
         <v>22</v>
       </c>
       <c r="F18" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="H18" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="BF18" t="s">
         <v>23</v>
       </c>
       <c r="BG18" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="19" spans="4:59" x14ac:dyDescent="0.25">
@@ -8921,13 +8927,13 @@
         <v>23</v>
       </c>
       <c r="F19" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="BF19" t="s">
         <v>24</v>
       </c>
       <c r="BG19" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="20" spans="4:59" x14ac:dyDescent="0.25">
@@ -8935,13 +8941,13 @@
         <v>24</v>
       </c>
       <c r="F20" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="BF20" t="s">
         <v>25</v>
       </c>
       <c r="BG20" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="21" spans="4:59" x14ac:dyDescent="0.25">
@@ -8952,7 +8958,7 @@
         <v>26</v>
       </c>
       <c r="BG21" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="22" spans="4:59" x14ac:dyDescent="0.25">
@@ -8963,7 +8969,7 @@
         <v>27</v>
       </c>
       <c r="BG22" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="23" spans="4:59" x14ac:dyDescent="0.25">

--- a/static/docs/AMA_uitslagen amateuvoetbal 2025-2026 definitief.xlsx
+++ b/static/docs/AMA_uitslagen amateuvoetbal 2025-2026 definitief.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mediahuis-my.sharepoint.com/personal/torsten_faruhn_delimburger_nl/Documents/Torsten/CUE Print/amateur- en regiosport nieuwe stijl/uitslagendienst/amateurvoetbal/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="112" documentId="8_{F6EDDE6E-FDD8-41E1-97DF-2A01485E9FFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1AC8C493-21C7-4729-A1CB-AF004EDF4EB9}"/>
+  <xr:revisionPtr revIDLastSave="114" documentId="8_{F6EDDE6E-FDD8-41E1-97DF-2A01485E9FFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E33B6170-D3CA-46BE-BCAF-F01FA096DCEA}"/>
   <bookViews>
-    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INVOER" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="863" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="313">
   <si>
     <t>KLASSE</t>
   </si>
@@ -358,9 +358,6 @@
   </si>
   <si>
     <t>RKHBS</t>
-  </si>
-  <si>
-    <t>Horn</t>
   </si>
   <si>
     <t>H.B.S.V.</t>
@@ -7676,14 +7673,24 @@
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="F131:H131"/>
-    <mergeCell ref="I131:K131"/>
-    <mergeCell ref="F79:H79"/>
-    <mergeCell ref="I79:K79"/>
-    <mergeCell ref="F92:H92"/>
-    <mergeCell ref="I92:K92"/>
-    <mergeCell ref="F105:H105"/>
-    <mergeCell ref="I105:K105"/>
+    <mergeCell ref="F235:H235"/>
+    <mergeCell ref="I235:K235"/>
+    <mergeCell ref="F248:H248"/>
+    <mergeCell ref="I248:K248"/>
+    <mergeCell ref="F261:H261"/>
+    <mergeCell ref="I261:K261"/>
+    <mergeCell ref="F196:H196"/>
+    <mergeCell ref="I196:K196"/>
+    <mergeCell ref="F209:H209"/>
+    <mergeCell ref="I209:K209"/>
+    <mergeCell ref="F222:H222"/>
+    <mergeCell ref="I222:K222"/>
+    <mergeCell ref="F157:H157"/>
+    <mergeCell ref="I157:K157"/>
+    <mergeCell ref="F170:H170"/>
+    <mergeCell ref="I170:K170"/>
+    <mergeCell ref="F183:H183"/>
+    <mergeCell ref="I183:K183"/>
     <mergeCell ref="F144:H144"/>
     <mergeCell ref="I144:K144"/>
     <mergeCell ref="F1:H1"/>
@@ -7700,24 +7707,14 @@
     <mergeCell ref="I66:K66"/>
     <mergeCell ref="F118:H118"/>
     <mergeCell ref="I118:K118"/>
-    <mergeCell ref="F157:H157"/>
-    <mergeCell ref="I157:K157"/>
-    <mergeCell ref="F170:H170"/>
-    <mergeCell ref="I170:K170"/>
-    <mergeCell ref="F183:H183"/>
-    <mergeCell ref="I183:K183"/>
-    <mergeCell ref="F196:H196"/>
-    <mergeCell ref="I196:K196"/>
-    <mergeCell ref="F209:H209"/>
-    <mergeCell ref="I209:K209"/>
-    <mergeCell ref="F222:H222"/>
-    <mergeCell ref="I222:K222"/>
-    <mergeCell ref="F235:H235"/>
-    <mergeCell ref="I235:K235"/>
-    <mergeCell ref="F248:H248"/>
-    <mergeCell ref="I248:K248"/>
-    <mergeCell ref="F261:H261"/>
-    <mergeCell ref="I261:K261"/>
+    <mergeCell ref="F131:H131"/>
+    <mergeCell ref="I131:K131"/>
+    <mergeCell ref="F79:H79"/>
+    <mergeCell ref="I79:K79"/>
+    <mergeCell ref="F92:H92"/>
+    <mergeCell ref="I92:K92"/>
+    <mergeCell ref="F105:H105"/>
+    <mergeCell ref="I105:K105"/>
   </mergeCells>
   <dataValidations count="24">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1 B131 B27 B40 B53 B66 B79 B92 B105 B118 B14 B144 B157 B170 B183 B196 B209 B222 B235 B248 B261" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -7936,7 +7933,7 @@
       </c>
       <c r="B2" s="1"/>
       <c r="D2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="BF2" t="s">
         <v>7</v>
@@ -7986,7 +7983,7 @@
         <v>42</v>
       </c>
       <c r="AD3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AF3" t="s">
         <v>44</v>
@@ -8039,7 +8036,7 @@
         <v>57</v>
       </c>
       <c r="P4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="R4" t="s">
         <v>58</v>
@@ -8137,7 +8134,7 @@
         <v>64</v>
       </c>
       <c r="AF5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AH5" t="s">
         <v>87</v>
@@ -8199,46 +8196,46 @@
         <v>103</v>
       </c>
       <c r="X6" t="s">
+        <v>124</v>
+      </c>
+      <c r="Z6" t="s">
         <v>104</v>
       </c>
-      <c r="Z6" t="s">
+      <c r="AB6" t="s">
         <v>105</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>106</v>
       </c>
       <c r="AD6" t="s">
         <v>86</v>
       </c>
       <c r="AF6" t="s">
+        <v>107</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>311</v>
+      </c>
+      <c r="AJ6" t="s">
         <v>108</v>
       </c>
-      <c r="AH6" t="s">
-        <v>312</v>
-      </c>
-      <c r="AJ6" t="s">
+      <c r="AL6" t="s">
         <v>109</v>
       </c>
-      <c r="AL6" t="s">
+      <c r="AN6" t="s">
         <v>110</v>
       </c>
-      <c r="AN6" t="s">
+      <c r="AP6" t="s">
         <v>111</v>
       </c>
-      <c r="AP6" t="s">
+      <c r="AR6" t="s">
         <v>112</v>
       </c>
-      <c r="AR6" t="s">
+      <c r="AT6" t="s">
         <v>113</v>
-      </c>
-      <c r="AT6" t="s">
-        <v>114</v>
       </c>
       <c r="BF6" t="s">
         <v>11</v>
       </c>
       <c r="BG6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:59" x14ac:dyDescent="0.25">
@@ -8246,73 +8243,73 @@
         <v>11</v>
       </c>
       <c r="F7" t="s">
+        <v>115</v>
+      </c>
+      <c r="H7" t="s">
         <v>116</v>
       </c>
-      <c r="H7" t="s">
+      <c r="J7" t="s">
         <v>117</v>
       </c>
-      <c r="J7" t="s">
+      <c r="L7" t="s">
         <v>118</v>
       </c>
-      <c r="L7" t="s">
+      <c r="N7" t="s">
         <v>119</v>
       </c>
-      <c r="N7" t="s">
+      <c r="P7" t="s">
         <v>120</v>
       </c>
-      <c r="P7" t="s">
+      <c r="R7" t="s">
         <v>121</v>
       </c>
-      <c r="R7" t="s">
+      <c r="T7" t="s">
         <v>122</v>
       </c>
-      <c r="T7" t="s">
+      <c r="V7" t="s">
         <v>123</v>
       </c>
-      <c r="V7" t="s">
-        <v>124</v>
-      </c>
       <c r="X7" t="s">
+        <v>145</v>
+      </c>
+      <c r="Z7" t="s">
         <v>125</v>
       </c>
-      <c r="Z7" t="s">
-        <v>126</v>
-      </c>
       <c r="AB7" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AD7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AF7" t="s">
+        <v>127</v>
+      </c>
+      <c r="AH7" t="s">
         <v>128</v>
       </c>
-      <c r="AH7" t="s">
+      <c r="AJ7" t="s">
         <v>129</v>
       </c>
-      <c r="AJ7" t="s">
+      <c r="AL7" t="s">
         <v>130</v>
       </c>
-      <c r="AL7" t="s">
+      <c r="AN7" t="s">
         <v>131</v>
       </c>
-      <c r="AN7" t="s">
+      <c r="AP7" t="s">
         <v>132</v>
       </c>
-      <c r="AP7" t="s">
+      <c r="AR7" t="s">
         <v>133</v>
       </c>
-      <c r="AR7" t="s">
+      <c r="AT7" t="s">
         <v>134</v>
-      </c>
-      <c r="AT7" t="s">
-        <v>135</v>
       </c>
       <c r="BF7" t="s">
         <v>12</v>
       </c>
       <c r="BG7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:59" x14ac:dyDescent="0.25">
@@ -8320,73 +8317,73 @@
         <v>12</v>
       </c>
       <c r="F8" t="s">
+        <v>136</v>
+      </c>
+      <c r="H8" t="s">
         <v>137</v>
       </c>
-      <c r="H8" t="s">
+      <c r="J8" t="s">
         <v>138</v>
       </c>
-      <c r="J8" t="s">
+      <c r="L8" t="s">
         <v>139</v>
       </c>
-      <c r="L8" t="s">
+      <c r="N8" t="s">
         <v>140</v>
       </c>
-      <c r="N8" t="s">
+      <c r="P8" t="s">
         <v>141</v>
       </c>
-      <c r="P8" t="s">
+      <c r="R8" t="s">
         <v>142</v>
       </c>
-      <c r="R8" t="s">
+      <c r="T8" t="s">
         <v>143</v>
       </c>
-      <c r="T8" t="s">
+      <c r="V8" t="s">
         <v>144</v>
       </c>
-      <c r="V8" t="s">
-        <v>145</v>
-      </c>
       <c r="X8" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="Z8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AB8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AD8" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AF8" t="s">
+        <v>149</v>
+      </c>
+      <c r="AH8" t="s">
         <v>150</v>
       </c>
-      <c r="AH8" t="s">
+      <c r="AJ8" t="s">
         <v>151</v>
       </c>
-      <c r="AJ8" t="s">
+      <c r="AL8" t="s">
         <v>152</v>
       </c>
-      <c r="AL8" t="s">
+      <c r="AN8" t="s">
         <v>153</v>
       </c>
-      <c r="AN8" t="s">
+      <c r="AP8" t="s">
         <v>154</v>
       </c>
-      <c r="AP8" t="s">
+      <c r="AR8" t="s">
         <v>155</v>
       </c>
-      <c r="AR8" t="s">
+      <c r="AT8" t="s">
         <v>156</v>
-      </c>
-      <c r="AT8" t="s">
-        <v>157</v>
       </c>
       <c r="BF8" t="s">
         <v>13</v>
       </c>
       <c r="BG8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="9" spans="1:59" x14ac:dyDescent="0.25">
@@ -8394,67 +8391,67 @@
         <v>13</v>
       </c>
       <c r="F9" t="s">
+        <v>158</v>
+      </c>
+      <c r="H9" t="s">
         <v>159</v>
       </c>
-      <c r="H9" t="s">
+      <c r="J9" t="s">
         <v>160</v>
       </c>
-      <c r="J9" t="s">
+      <c r="L9" t="s">
         <v>161</v>
       </c>
-      <c r="L9" t="s">
+      <c r="N9" t="s">
         <v>162</v>
       </c>
-      <c r="N9" t="s">
+      <c r="P9" t="s">
         <v>163</v>
       </c>
-      <c r="P9" t="s">
+      <c r="R9" t="s">
         <v>164</v>
       </c>
-      <c r="R9" t="s">
+      <c r="T9" t="s">
         <v>165</v>
       </c>
-      <c r="T9" t="s">
+      <c r="V9" t="s">
         <v>166</v>
       </c>
-      <c r="V9" t="s">
-        <v>167</v>
-      </c>
       <c r="X9" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="Z9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AB9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AD9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AF9" t="s">
+        <v>171</v>
+      </c>
+      <c r="AH9" t="s">
         <v>172</v>
       </c>
-      <c r="AH9" t="s">
+      <c r="AJ9" t="s">
         <v>173</v>
       </c>
-      <c r="AJ9" t="s">
+      <c r="AL9" t="s">
         <v>174</v>
       </c>
-      <c r="AL9" t="s">
+      <c r="AN9" t="s">
         <v>175</v>
       </c>
-      <c r="AN9" t="s">
+      <c r="AP9" t="s">
         <v>176</v>
       </c>
-      <c r="AP9" t="s">
+      <c r="AR9" t="s">
         <v>177</v>
       </c>
-      <c r="AR9" t="s">
+      <c r="AT9" t="s">
         <v>178</v>
-      </c>
-      <c r="AT9" t="s">
-        <v>179</v>
       </c>
       <c r="BF9" t="s">
         <v>14</v>
@@ -8468,73 +8465,73 @@
         <v>14</v>
       </c>
       <c r="F10" t="s">
+        <v>179</v>
+      </c>
+      <c r="H10" t="s">
         <v>180</v>
       </c>
-      <c r="H10" t="s">
+      <c r="J10" t="s">
         <v>181</v>
       </c>
-      <c r="J10" t="s">
+      <c r="L10" t="s">
         <v>182</v>
       </c>
-      <c r="L10" t="s">
+      <c r="N10" t="s">
         <v>183</v>
       </c>
-      <c r="N10" t="s">
+      <c r="P10" t="s">
         <v>184</v>
       </c>
-      <c r="P10" t="s">
+      <c r="R10" t="s">
         <v>185</v>
       </c>
-      <c r="R10" t="s">
+      <c r="T10" t="s">
         <v>186</v>
       </c>
-      <c r="T10" t="s">
+      <c r="V10" t="s">
         <v>187</v>
       </c>
-      <c r="V10" t="s">
-        <v>188</v>
-      </c>
       <c r="X10" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="Z10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AB10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AD10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AF10" t="s">
+        <v>192</v>
+      </c>
+      <c r="AH10" t="s">
         <v>193</v>
       </c>
-      <c r="AH10" t="s">
+      <c r="AJ10" t="s">
         <v>194</v>
       </c>
-      <c r="AJ10" t="s">
+      <c r="AL10" t="s">
         <v>195</v>
       </c>
-      <c r="AL10" t="s">
+      <c r="AN10" t="s">
         <v>196</v>
       </c>
-      <c r="AN10" t="s">
+      <c r="AP10" t="s">
         <v>197</v>
       </c>
-      <c r="AP10" t="s">
+      <c r="AR10" t="s">
         <v>198</v>
       </c>
-      <c r="AR10" t="s">
-        <v>199</v>
-      </c>
       <c r="AT10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="BF10" t="s">
         <v>15</v>
       </c>
       <c r="BG10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11" spans="1:59" x14ac:dyDescent="0.25">
@@ -8542,73 +8539,73 @@
         <v>15</v>
       </c>
       <c r="F11" t="s">
+        <v>200</v>
+      </c>
+      <c r="H11" t="s">
         <v>201</v>
       </c>
-      <c r="H11" t="s">
+      <c r="J11" t="s">
         <v>202</v>
       </c>
-      <c r="J11" t="s">
+      <c r="L11" t="s">
         <v>203</v>
       </c>
-      <c r="L11" t="s">
+      <c r="N11" t="s">
         <v>204</v>
       </c>
-      <c r="N11" t="s">
+      <c r="P11" t="s">
         <v>205</v>
       </c>
-      <c r="P11" t="s">
+      <c r="R11" t="s">
         <v>206</v>
       </c>
-      <c r="R11" t="s">
+      <c r="T11" t="s">
         <v>207</v>
       </c>
-      <c r="T11" t="s">
+      <c r="V11" t="s">
         <v>208</v>
       </c>
-      <c r="V11" t="s">
-        <v>209</v>
-      </c>
       <c r="X11" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="Z11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AB11" t="s">
+        <v>211</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>170</v>
+      </c>
+      <c r="AF11" t="s">
         <v>212</v>
       </c>
-      <c r="AD11" t="s">
-        <v>171</v>
-      </c>
-      <c r="AF11" t="s">
+      <c r="AH11" t="s">
         <v>213</v>
       </c>
-      <c r="AH11" t="s">
+      <c r="AJ11" t="s">
         <v>214</v>
       </c>
-      <c r="AJ11" t="s">
+      <c r="AL11" t="s">
         <v>215</v>
       </c>
-      <c r="AL11" t="s">
+      <c r="AN11" t="s">
         <v>216</v>
       </c>
-      <c r="AN11" t="s">
+      <c r="AP11" t="s">
         <v>217</v>
       </c>
-      <c r="AP11" t="s">
+      <c r="AR11" t="s">
         <v>218</v>
       </c>
-      <c r="AR11" t="s">
+      <c r="AT11" t="s">
         <v>219</v>
-      </c>
-      <c r="AT11" t="s">
-        <v>220</v>
       </c>
       <c r="BF11" t="s">
         <v>16</v>
       </c>
       <c r="BG11" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="12" spans="1:59" x14ac:dyDescent="0.25">
@@ -8616,73 +8613,73 @@
         <v>16</v>
       </c>
       <c r="F12" t="s">
+        <v>221</v>
+      </c>
+      <c r="H12" t="s">
+        <v>218</v>
+      </c>
+      <c r="J12" t="s">
         <v>222</v>
       </c>
-      <c r="H12" t="s">
-        <v>219</v>
-      </c>
-      <c r="J12" t="s">
+      <c r="L12" t="s">
+        <v>308</v>
+      </c>
+      <c r="N12" t="s">
         <v>223</v>
       </c>
-      <c r="L12" t="s">
-        <v>309</v>
-      </c>
-      <c r="N12" t="s">
+      <c r="P12" t="s">
         <v>224</v>
       </c>
-      <c r="P12" t="s">
+      <c r="R12" t="s">
         <v>225</v>
       </c>
-      <c r="R12" t="s">
+      <c r="T12" t="s">
         <v>226</v>
       </c>
-      <c r="T12" t="s">
+      <c r="V12" t="s">
         <v>227</v>
       </c>
-      <c r="V12" t="s">
-        <v>228</v>
-      </c>
       <c r="X12" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="Z12" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AB12" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AD12" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AF12" t="s">
+        <v>232</v>
+      </c>
+      <c r="AH12" t="s">
         <v>233</v>
       </c>
-      <c r="AH12" t="s">
+      <c r="AJ12" t="s">
         <v>234</v>
       </c>
-      <c r="AJ12" t="s">
+      <c r="AL12" t="s">
         <v>235</v>
       </c>
-      <c r="AL12" t="s">
+      <c r="AN12" t="s">
         <v>236</v>
       </c>
-      <c r="AN12" t="s">
+      <c r="AP12" t="s">
         <v>237</v>
-      </c>
-      <c r="AP12" t="s">
-        <v>238</v>
       </c>
       <c r="AR12" t="s">
         <v>103</v>
       </c>
       <c r="AT12" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="BF12" t="s">
         <v>17</v>
       </c>
       <c r="BG12" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="13" spans="1:59" x14ac:dyDescent="0.25">
@@ -8690,73 +8687,73 @@
         <v>17</v>
       </c>
       <c r="F13" t="s">
+        <v>240</v>
+      </c>
+      <c r="H13" t="s">
+        <v>309</v>
+      </c>
+      <c r="J13" t="s">
+        <v>198</v>
+      </c>
+      <c r="L13" t="s">
         <v>241</v>
       </c>
-      <c r="H13" t="s">
-        <v>310</v>
-      </c>
-      <c r="J13" t="s">
-        <v>199</v>
-      </c>
-      <c r="L13" t="s">
+      <c r="N13" t="s">
         <v>242</v>
       </c>
-      <c r="N13" t="s">
+      <c r="P13" t="s">
         <v>243</v>
       </c>
-      <c r="P13" t="s">
+      <c r="R13" t="s">
         <v>244</v>
       </c>
-      <c r="R13" t="s">
+      <c r="T13" t="s">
         <v>245</v>
       </c>
-      <c r="T13" t="s">
+      <c r="V13" t="s">
         <v>246</v>
       </c>
-      <c r="V13" t="s">
-        <v>247</v>
-      </c>
       <c r="X13" t="s">
-        <v>248</v>
+        <v>267</v>
       </c>
       <c r="Z13" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AB13" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AD13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AF13" t="s">
+        <v>251</v>
+      </c>
+      <c r="AH13" t="s">
         <v>252</v>
       </c>
-      <c r="AH13" t="s">
+      <c r="AJ13" t="s">
         <v>253</v>
       </c>
-      <c r="AJ13" t="s">
+      <c r="AL13" t="s">
         <v>254</v>
       </c>
-      <c r="AL13" t="s">
+      <c r="AN13" t="s">
         <v>255</v>
       </c>
-      <c r="AN13" t="s">
+      <c r="AP13" t="s">
         <v>256</v>
       </c>
-      <c r="AP13" t="s">
+      <c r="AR13" t="s">
+        <v>312</v>
+      </c>
+      <c r="AT13" t="s">
         <v>257</v>
-      </c>
-      <c r="AR13" t="s">
-        <v>313</v>
-      </c>
-      <c r="AT13" t="s">
-        <v>258</v>
       </c>
       <c r="BF13" t="s">
         <v>18</v>
       </c>
       <c r="BG13" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="14" spans="1:59" x14ac:dyDescent="0.25">
@@ -8764,67 +8761,64 @@
         <v>18</v>
       </c>
       <c r="F14" t="s">
+        <v>259</v>
+      </c>
+      <c r="H14" t="s">
         <v>260</v>
       </c>
-      <c r="H14" t="s">
+      <c r="J14" t="s">
         <v>261</v>
       </c>
-      <c r="J14" t="s">
+      <c r="L14" t="s">
         <v>262</v>
       </c>
-      <c r="L14" t="s">
+      <c r="N14" t="s">
         <v>263</v>
       </c>
-      <c r="N14" t="s">
+      <c r="P14" t="s">
         <v>264</v>
       </c>
-      <c r="P14" t="s">
+      <c r="R14" t="s">
         <v>265</v>
       </c>
-      <c r="R14" t="s">
+      <c r="T14" t="s">
         <v>266</v>
       </c>
-      <c r="T14" t="s">
-        <v>267</v>
-      </c>
-      <c r="X14" t="s">
+      <c r="Z14" t="s">
+        <v>248</v>
+      </c>
+      <c r="AB14" t="s">
         <v>268</v>
       </c>
-      <c r="Z14" t="s">
-        <v>249</v>
-      </c>
-      <c r="AB14" t="s">
+      <c r="AD14" t="s">
         <v>269</v>
       </c>
-      <c r="AD14" t="s">
+      <c r="AF14" t="s">
         <v>270</v>
       </c>
-      <c r="AF14" t="s">
+      <c r="AH14" t="s">
         <v>271</v>
       </c>
-      <c r="AH14" t="s">
+      <c r="AL14" t="s">
+        <v>306</v>
+      </c>
+      <c r="AN14" t="s">
         <v>272</v>
       </c>
-      <c r="AL14" t="s">
-        <v>307</v>
-      </c>
-      <c r="AN14" t="s">
+      <c r="AP14" t="s">
         <v>273</v>
       </c>
-      <c r="AP14" t="s">
+      <c r="AR14" t="s">
         <v>274</v>
       </c>
-      <c r="AR14" t="s">
+      <c r="AT14" t="s">
         <v>275</v>
-      </c>
-      <c r="AT14" t="s">
-        <v>276</v>
       </c>
       <c r="BF14" t="s">
         <v>19</v>
       </c>
       <c r="BG14" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15" spans="1:59" x14ac:dyDescent="0.25">
@@ -8832,31 +8826,31 @@
         <v>19</v>
       </c>
       <c r="F15" t="s">
+        <v>277</v>
+      </c>
+      <c r="H15" t="s">
         <v>278</v>
       </c>
-      <c r="H15" t="s">
+      <c r="J15" t="s">
         <v>279</v>
       </c>
-      <c r="J15" t="s">
+      <c r="L15" t="s">
         <v>280</v>
       </c>
-      <c r="L15" t="s">
+      <c r="N15" t="s">
         <v>281</v>
       </c>
-      <c r="N15" t="s">
+      <c r="P15" t="s">
         <v>282</v>
       </c>
-      <c r="P15" t="s">
+      <c r="R15" t="s">
         <v>283</v>
-      </c>
-      <c r="R15" t="s">
-        <v>284</v>
       </c>
       <c r="BF15" t="s">
         <v>20</v>
       </c>
       <c r="BG15" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="16" spans="1:59" x14ac:dyDescent="0.25">
@@ -8864,28 +8858,28 @@
         <v>20</v>
       </c>
       <c r="F16" t="s">
+        <v>285</v>
+      </c>
+      <c r="H16" t="s">
         <v>286</v>
       </c>
-      <c r="H16" t="s">
+      <c r="J16" t="s">
         <v>287</v>
       </c>
-      <c r="J16" t="s">
+      <c r="L16" t="s">
         <v>288</v>
       </c>
-      <c r="L16" t="s">
+      <c r="N16" t="s">
         <v>289</v>
       </c>
-      <c r="N16" t="s">
+      <c r="R16" t="s">
         <v>290</v>
-      </c>
-      <c r="R16" t="s">
-        <v>291</v>
       </c>
       <c r="BF16" t="s">
         <v>21</v>
       </c>
       <c r="BG16" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="17" spans="4:59" x14ac:dyDescent="0.25">
@@ -8893,16 +8887,16 @@
         <v>21</v>
       </c>
       <c r="F17" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H17" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="BF17" t="s">
         <v>22</v>
       </c>
       <c r="BG17" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="18" spans="4:59" x14ac:dyDescent="0.25">
@@ -8910,16 +8904,16 @@
         <v>22</v>
       </c>
       <c r="F18" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H18" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="BF18" t="s">
         <v>23</v>
       </c>
       <c r="BG18" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="19" spans="4:59" x14ac:dyDescent="0.25">
@@ -8927,13 +8921,13 @@
         <v>23</v>
       </c>
       <c r="F19" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="BF19" t="s">
         <v>24</v>
       </c>
       <c r="BG19" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="20" spans="4:59" x14ac:dyDescent="0.25">
@@ -8941,13 +8935,13 @@
         <v>24</v>
       </c>
       <c r="F20" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="BF20" t="s">
         <v>25</v>
       </c>
       <c r="BG20" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="21" spans="4:59" x14ac:dyDescent="0.25">
@@ -8958,7 +8952,7 @@
         <v>26</v>
       </c>
       <c r="BG21" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="22" spans="4:59" x14ac:dyDescent="0.25">
@@ -8969,7 +8963,7 @@
         <v>27</v>
       </c>
       <c r="BG22" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="23" spans="4:59" x14ac:dyDescent="0.25">
